--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$92</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$96</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$91</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4168,7 +4168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 32.8, "op_wape_pct": 137.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 591.46, "rev_act": 772.26, "op_pred": -27.24, "op_act": 23.73}, {"q": "2025Q4", "rev_pred": 730.41, "rev_act": 1243.15, "op_pred": -33.64, "op_act": 198.56}, {"q": "2026Q1", "rev_pred": 411.16, "rev_act": 647.24, "op_pred": -18.93, "op_act": 5.93}, {"q": "2026Q2", "rev_pred": 708.83, "rev_act": 972.46, "op_pred": -32.64, "op_act": 71.36}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 32.8, "op_wape_pct": 137.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 591.46, "rev_act": 772.26, "op_pred": -27.24, "op_act": 23.73}, {"q": "2025Q4", "rev_pred": 730.41, "rev_act": 1243.15, "op_pred": -33.64, "op_act": 198.56}, {"q": "2026Q1", "rev_pred": 411.16, "rev_act": 647.24, "op_pred": -18.93, "op_act": 5.93}, {"q": "2026Q2", "rev_pred": 708.83, "rev_act": 972.46, "op_pred": -32.64, "op_act": 71.36}]}</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO92"/>
+  <dimension ref="A1:AO96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15884,78 +15884,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E72" s="18" t="n">
-        <v>572.6</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F72" s="9" t="n"/>
-      <c r="G72" s="18" t="n">
-        <v>-10250.78</v>
-      </c>
-      <c r="H72" s="18" t="n">
-        <v>-303.94</v>
-      </c>
-      <c r="I72" s="18" t="n">
-        <v>1158.22</v>
-      </c>
-      <c r="J72" s="18" t="n">
-        <v>-16685.78</v>
-      </c>
-      <c r="K72" s="35" t="n">
-        <v>-26082.28</v>
-      </c>
-      <c r="L72" s="18" t="n">
-        <v>-15921.34</v>
-      </c>
-      <c r="M72" s="18" t="n">
-        <v>7069.53</v>
-      </c>
-      <c r="N72" s="18" t="n">
-        <v>18612.77</v>
-      </c>
-      <c r="O72" s="18" t="n">
-        <v>20057.32</v>
-      </c>
-      <c r="P72" s="35" t="n">
-        <v>29818.28</v>
-      </c>
-      <c r="Q72" s="18" t="n">
-        <v>17964.21</v>
-      </c>
-      <c r="R72" s="18" t="n">
-        <v>-2223.68</v>
-      </c>
-      <c r="S72" s="18" t="n">
-        <v>-17695.02</v>
-      </c>
-      <c r="T72" s="18" t="n">
-        <v>5911.45</v>
-      </c>
-      <c r="U72" s="35" t="n">
-        <v>3956.96</v>
-      </c>
-      <c r="V72" s="18" t="n">
-        <v>11807.24</v>
-      </c>
-      <c r="W72" s="18" t="n">
-        <v>-33423.21</v>
-      </c>
-      <c r="X72" s="18" t="n">
-        <v>-7706.54</v>
-      </c>
-      <c r="Y72" s="18" t="n">
-        <v>11083.29</v>
-      </c>
-      <c r="Z72" s="35" t="n">
-        <v>-18239.22</v>
-      </c>
-      <c r="AA72" s="18" t="n">
-        <v>17078.09</v>
-      </c>
+      <c r="K72" s="9" t="n"/>
+      <c r="P72" s="9" t="n"/>
+      <c r="U72" s="9" t="n"/>
+      <c r="Z72" s="9" t="n"/>
       <c r="AB72" s="19" t="n">
-        <v>-4214.92</v>
+        <v>257.97</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -15977,78 +15915,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>60.86</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F73" s="9" t="n"/>
-      <c r="G73" s="18" t="n">
-        <v>277.57</v>
-      </c>
-      <c r="H73" s="18" t="n">
-        <v>260.07</v>
-      </c>
-      <c r="I73" s="18" t="n">
-        <v>177.87</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>168.76</v>
-      </c>
-      <c r="K73" s="35" t="n">
-        <v>884.27</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>232.8</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>125.83</v>
-      </c>
-      <c r="N73" s="18" t="n">
-        <v>399.25</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>1046.42</v>
-      </c>
-      <c r="P73" s="35" t="n">
-        <v>1804.3</v>
-      </c>
-      <c r="Q73" s="18" t="n">
-        <v>1110.31</v>
-      </c>
-      <c r="R73" s="18" t="n">
-        <v>1106.02</v>
-      </c>
-      <c r="S73" s="18" t="n">
-        <v>1139.32</v>
-      </c>
-      <c r="T73" s="18" t="n">
-        <v>484.46</v>
-      </c>
-      <c r="U73" s="35" t="n">
-        <v>3840.11</v>
-      </c>
-      <c r="V73" s="18" t="n">
-        <v>242.33</v>
-      </c>
-      <c r="W73" s="18" t="n">
-        <v>349.7</v>
-      </c>
-      <c r="X73" s="18" t="n">
-        <v>298.93</v>
-      </c>
-      <c r="Y73" s="18" t="n">
-        <v>338.41</v>
-      </c>
-      <c r="Z73" s="35" t="n">
-        <v>1229.37</v>
-      </c>
-      <c r="AA73" s="18" t="n">
-        <v>294.16</v>
-      </c>
+      <c r="K73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="U73" s="9" t="n"/>
+      <c r="Z73" s="9" t="n"/>
       <c r="AB73" s="19" t="n">
-        <v>204.1</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -16070,48 +15946,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>-219.24</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F74" s="9" t="n"/>
-      <c r="G74" s="18" t="n">
-        <v>-241.35</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>-376.13</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <v>-486.56</v>
-      </c>
-      <c r="J74" s="18" t="n">
-        <v>-673.73</v>
-      </c>
-      <c r="K74" s="35" t="n">
-        <v>-1777.77</v>
-      </c>
-      <c r="L74" s="18" t="n">
-        <v>-1061.27</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>-1285.17</v>
-      </c>
+      <c r="K74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
       <c r="U74" s="9" t="n"/>
-      <c r="X74" s="18" t="n">
-        <v>-1253.32</v>
-      </c>
-      <c r="Y74" s="18" t="n">
-        <v>-1379.7</v>
-      </c>
       <c r="Z74" s="9" t="n"/>
-      <c r="AA74" s="18" t="n">
-        <v>-1318.4</v>
-      </c>
       <c r="AB74" s="19" t="n">
-        <v>-1424.13</v>
+        <v>1742.09</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -16133,30 +15977,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>0</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
-      <c r="I75" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="18" t="n">
-        <v>19.58</v>
-      </c>
       <c r="K75" s="9" t="n"/>
-      <c r="L75" s="18" t="n">
-        <v>9.789999999999999</v>
-      </c>
       <c r="P75" s="9" t="n"/>
-      <c r="T75" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="U75" s="9" t="n"/>
       <c r="Z75" s="9" t="n"/>
-      <c r="AB75" s="5" t="n"/>
+      <c r="AB75" s="19" t="n">
+        <v>-1484.12</v>
+      </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
@@ -16177,78 +16008,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-516.3</v>
+        <v>572.6</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-100.78</v>
+        <v>-10250.78</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-209.65</v>
+        <v>-303.94</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-20.22</v>
+        <v>1158.22</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-185.44</v>
+        <v>-16685.78</v>
       </c>
       <c r="K76" s="35" t="n">
-        <v>-516.09</v>
+        <v>-26082.28</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-273.41</v>
+        <v>-15921.34</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-1476.65</v>
+        <v>7069.53</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-54.65</v>
+        <v>18612.77</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-645.9400000000001</v>
+        <v>20057.32</v>
       </c>
       <c r="P76" s="35" t="n">
-        <v>-2450.65</v>
+        <v>29818.28</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>-886.8099999999999</v>
+        <v>17964.21</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>-126.38</v>
+        <v>-2223.68</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>-257.21</v>
+        <v>-17695.02</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>294.56</v>
+        <v>5911.45</v>
       </c>
       <c r="U76" s="35" t="n">
-        <v>-975.84</v>
+        <v>3956.96</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>-637.63</v>
+        <v>11807.24</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>941.97</v>
+        <v>-33423.21</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>-244.62</v>
+        <v>-7706.54</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>-131.8</v>
+        <v>11083.29</v>
       </c>
       <c r="Z76" s="35" t="n">
-        <v>-72.08</v>
+        <v>-18239.22</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>-1126</v>
+        <v>17078.09</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>-2045.49</v>
+        <v>-4214.92</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -16270,78 +16101,78 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-2905.39</v>
+        <v>60.86</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>-7074.62</v>
+        <v>277.57</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-539.5</v>
+        <v>260.07</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-14168.85</v>
+        <v>177.87</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-5794.54</v>
+        <v>168.76</v>
       </c>
       <c r="K77" s="35" t="n">
-        <v>-27577.51</v>
+        <v>884.27</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-1735.47</v>
+        <v>232.8</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-17467.06</v>
+        <v>125.83</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-61014.02</v>
+        <v>399.25</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-7337.33</v>
+        <v>1046.42</v>
       </c>
       <c r="P77" s="35" t="n">
-        <v>-87553.88</v>
+        <v>1804.3</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>-29623.27</v>
+        <v>1110.31</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>-12644.71</v>
+        <v>1106.02</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>19558.09</v>
+        <v>1139.32</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>-3825</v>
+        <v>484.46</v>
       </c>
       <c r="U77" s="35" t="n">
-        <v>-26534.89</v>
+        <v>3840.11</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>-6387.86</v>
+        <v>242.33</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>10860.28</v>
+        <v>349.7</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>-574.42</v>
+        <v>298.93</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>12248.11</v>
+        <v>338.41</v>
       </c>
       <c r="Z77" s="35" t="n">
-        <v>16146.11</v>
+        <v>1229.37</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>-14000.62</v>
+        <v>294.16</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>-10221.89</v>
+        <v>204.1</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -16363,68 +16194,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-0.71</v>
+        <v>-219.24</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>27</v>
+        <v>-241.35</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>0</v>
+        <v>-376.13</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>69.03</v>
+        <v>-486.56</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>0</v>
+        <v>-673.73</v>
       </c>
       <c r="K78" s="35" t="n">
-        <v>96.03</v>
+        <v>-1777.77</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>32.24</v>
+        <v>-1061.27</v>
+      </c>
+      <c r="M78" s="18" t="n">
+        <v>-1285.17</v>
       </c>
       <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="18" t="n">
-        <v>1117.11</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>71.64</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>2</v>
-      </c>
       <c r="U78" s="9" t="n"/>
-      <c r="V78" s="18" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="X78" s="18" t="n">
-        <v>0</v>
+        <v>-1253.32</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>4806.35</v>
-      </c>
-      <c r="Z78" s="35" t="n">
-        <v>4806.98</v>
-      </c>
+        <v>-1379.7</v>
+      </c>
+      <c r="Z78" s="9" t="n"/>
       <c r="AA78" s="18" t="n">
-        <v>0.17</v>
+        <v>-1318.4</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>0</v>
+        <v>-1424.13</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -16446,79 +16257,30 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>6461.63</v>
+        <v>0</v>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>7784.68</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>6647.6</v>
-      </c>
       <c r="I79" s="18" t="n">
-        <v>11955.85</v>
+        <v>0</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>11270.49</v>
-      </c>
-      <c r="K79" s="35" t="n">
-        <v>37658.62</v>
-      </c>
+        <v>19.58</v>
+      </c>
+      <c r="K79" s="9" t="n"/>
       <c r="L79" s="18" t="n">
-        <v>6854.3</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>4092.89</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>2945.81</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>2736.43</v>
-      </c>
-      <c r="P79" s="35" t="n">
-        <v>16629.43</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>5371.59</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>1350.59</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>2152.55</v>
-      </c>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="P79" s="9" t="n"/>
       <c r="T79" s="18" t="n">
-        <v>1179.42</v>
-      </c>
-      <c r="U79" s="35" t="n">
-        <v>10054.15</v>
-      </c>
-      <c r="V79" s="18" t="n">
-        <v>780.35</v>
-      </c>
-      <c r="W79" s="18" t="n">
-        <v>1037.95</v>
-      </c>
-      <c r="X79" s="18" t="n">
-        <v>9521.309999999999</v>
-      </c>
-      <c r="Y79" s="18" t="n">
-        <v>1197.69</v>
-      </c>
-      <c r="Z79" s="35" t="n">
-        <v>12537.3</v>
-      </c>
-      <c r="AA79" s="18" t="n">
-        <v>9342.389999999999</v>
-      </c>
-      <c r="AB79" s="19" t="n">
-        <v>7886.98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U79" s="9" t="n"/>
+      <c r="Z79" s="9" t="n"/>
+      <c r="AB79" s="5" t="n"/>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="11" t="n"/>
@@ -16539,78 +16301,78 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>7415.08</v>
+        <v>-516.3</v>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>8878.35</v>
+        <v>-100.78</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>8345.82</v>
+        <v>-209.65</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>13690.39</v>
+        <v>-20.22</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>13606.32</v>
+        <v>-185.44</v>
       </c>
       <c r="K80" s="35" t="n">
-        <v>44520.88</v>
+        <v>-516.09</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>8314.23</v>
+        <v>-273.41</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>5944.58</v>
+        <v>-1476.65</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>7201.86</v>
+        <v>-54.65</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>8864.24</v>
+        <v>-645.9400000000001</v>
       </c>
       <c r="P80" s="35" t="n">
-        <v>30324.91</v>
+        <v>-2450.65</v>
       </c>
       <c r="Q80" s="18" t="n">
-        <v>11888.35</v>
+        <v>-886.8099999999999</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>8806.139999999999</v>
+        <v>-126.38</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>5558.7</v>
+        <v>-257.21</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>3671.45</v>
+        <v>294.56</v>
       </c>
       <c r="U80" s="35" t="n">
-        <v>29924.64</v>
+        <v>-975.84</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>2626.09</v>
+        <v>-637.63</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>6172.2</v>
+        <v>941.97</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>14395.99</v>
+        <v>-244.62</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>8405.51</v>
+        <v>-131.8</v>
       </c>
       <c r="Z80" s="35" t="n">
-        <v>31599.79</v>
+        <v>-72.08</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>12964.28</v>
+        <v>-1126</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>10137.19</v>
+        <v>-2045.49</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -16632,78 +16394,78 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>953.45</v>
+        <v>-2905.39</v>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="18" t="n">
-        <v>1093.67</v>
+        <v>-7074.62</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>1698.22</v>
+        <v>-539.5</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>1734.54</v>
+        <v>-14168.85</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>2335.83</v>
+        <v>-5794.54</v>
       </c>
       <c r="K81" s="35" t="n">
-        <v>6862.26</v>
+        <v>-27577.51</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>1459.93</v>
+        <v>-1735.47</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>1851.69</v>
+        <v>-17467.06</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>4256.05</v>
+        <v>-61014.02</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>6127.81</v>
+        <v>-7337.33</v>
       </c>
       <c r="P81" s="35" t="n">
-        <v>13695.48</v>
+        <v>-87553.88</v>
       </c>
       <c r="Q81" s="18" t="n">
-        <v>6516.76</v>
+        <v>-29623.27</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>7455.55</v>
+        <v>-12644.71</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>3406.15</v>
+        <v>19558.09</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>2492.03</v>
+        <v>-3825</v>
       </c>
       <c r="U81" s="35" t="n">
-        <v>19870.49</v>
+        <v>-26534.89</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>1845.74</v>
+        <v>-6387.86</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>5134.25</v>
+        <v>10860.28</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>4874.68</v>
+        <v>-574.42</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>7207.82</v>
+        <v>12248.11</v>
       </c>
       <c r="Z81" s="35" t="n">
-        <v>19062.49</v>
+        <v>16146.11</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>3621.89</v>
+        <v>-14000.62</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>2250.21</v>
+        <v>-10221.89</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -16725,78 +16487,68 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>4861.65</v>
+        <v>-0.71</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>14727.4</v>
+        <v>27</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>-308.41</v>
+        <v>0</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>20160.95</v>
+        <v>69.03</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>21273.46</v>
+        <v>0</v>
       </c>
       <c r="K82" s="35" t="n">
-        <v>55853.4</v>
+        <v>96.03</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>11149.11</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>19205.63</v>
+        <v>17.87</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>62888.84</v>
+        <v>0</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>-4269.59</v>
-      </c>
-      <c r="P82" s="35" t="n">
-        <v>88973.99000000001</v>
-      </c>
+        <v>32.24</v>
+      </c>
+      <c r="P82" s="9" t="n"/>
       <c r="Q82" s="18" t="n">
-        <v>-4887.78</v>
+        <v>1117.11</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>5243.04</v>
+        <v>71.64</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>-5169.97</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-8646.799999999999</v>
-      </c>
-      <c r="U82" s="35" t="n">
-        <v>-13461.51</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U82" s="9" t="n"/>
       <c r="V82" s="18" t="n">
-        <v>-3440.56</v>
+        <v>0.63</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>16064.18</v>
+        <v>0</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>14746.44</v>
+        <v>0</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-14297.97</v>
+        <v>4806.35</v>
       </c>
       <c r="Z82" s="35" t="n">
-        <v>13072.09</v>
+        <v>4806.98</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-4867.03</v>
+        <v>0.17</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>7456.99</v>
+        <v>0</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -16818,70 +16570,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>19500.28</v>
+        <v>6461.63</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>19300</v>
+        <v>7784.68</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>39337.34</v>
+        <v>6647.6</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>13607.98</v>
+        <v>11955.85</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>32151.63</v>
+        <v>11270.49</v>
       </c>
       <c r="K83" s="35" t="n">
-        <v>104396.95</v>
+        <v>37658.62</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>47748</v>
+        <v>6854.3</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>36771.39</v>
+        <v>4092.89</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>38966.42</v>
+        <v>2945.81</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>0</v>
+        <v>2736.43</v>
       </c>
       <c r="P83" s="35" t="n">
-        <v>123485.81</v>
+        <v>16629.43</v>
+      </c>
+      <c r="Q83" s="18" t="n">
+        <v>5371.59</v>
+      </c>
+      <c r="R83" s="18" t="n">
+        <v>1350.59</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>45002.67</v>
+        <v>2152.55</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>17000</v>
-      </c>
-      <c r="U83" s="9" t="n"/>
+        <v>1179.42</v>
+      </c>
+      <c r="U83" s="35" t="n">
+        <v>10054.15</v>
+      </c>
       <c r="V83" s="18" t="n">
-        <v>261.95</v>
+        <v>780.35</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>24500</v>
+        <v>1037.95</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>0</v>
+        <v>9521.309999999999</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>43288.21</v>
+        <v>1197.69</v>
       </c>
       <c r="Z83" s="35" t="n">
-        <v>68050.16</v>
+        <v>12537.3</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>0</v>
+        <v>9342.389999999999</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>18299.9</v>
+        <v>7886.98</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -16903,78 +16663,78 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>14400.28</v>
+        <v>7415.08</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>10143.47</v>
+        <v>8878.35</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>36406.57</v>
+        <v>8345.82</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>0</v>
+        <v>13690.39</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>12905.26</v>
+        <v>13606.32</v>
       </c>
       <c r="K84" s="35" t="n">
-        <v>59455.3</v>
+        <v>44520.88</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>45704.37</v>
+        <v>8314.23</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>23638.07</v>
+        <v>5944.58</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>64500</v>
+        <v>7201.86</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>2981.26</v>
+        <v>8864.24</v>
       </c>
       <c r="P84" s="35" t="n">
-        <v>136823.7</v>
+        <v>30324.91</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>500</v>
+        <v>11888.35</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>540.0599999999999</v>
+        <v>8806.139999999999</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>47002.47</v>
+        <v>5558.7</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>24700</v>
+        <v>3671.45</v>
       </c>
       <c r="U84" s="35" t="n">
-        <v>72742.53</v>
+        <v>29924.64</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>261.95</v>
+        <v>2626.09</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>2500</v>
+        <v>6172.2</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>7416</v>
+        <v>14395.99</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>44204.21</v>
+        <v>8405.51</v>
       </c>
       <c r="Z84" s="35" t="n">
-        <v>54382.16</v>
+        <v>31599.79</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>416</v>
+        <v>12964.28</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>6715.9</v>
+        <v>10137.19</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -16996,78 +16756,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>486.55</v>
+        <v>953.45</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>547.58</v>
+        <v>1093.67</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>634.99</v>
+        <v>1698.22</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>692.52</v>
+        <v>1734.54</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>866.27</v>
+        <v>2335.83</v>
       </c>
       <c r="K85" s="35" t="n">
-        <v>2741.36</v>
+        <v>6862.26</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>811.03</v>
+        <v>1459.93</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>842.89</v>
+        <v>1851.69</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>857.5</v>
+        <v>4256.05</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>863.65</v>
+        <v>6127.81</v>
       </c>
       <c r="P85" s="35" t="n">
-        <v>3375.07</v>
+        <v>13695.48</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>1091.86</v>
+        <v>6516.76</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1228.2</v>
+        <v>7455.55</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>1219.79</v>
+        <v>3406.15</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>1333.44</v>
+        <v>2492.03</v>
       </c>
       <c r="U85" s="35" t="n">
-        <v>4873.29</v>
+        <v>19870.49</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>1320.22</v>
+        <v>1845.74</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>1290.28</v>
+        <v>5134.25</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>1280.38</v>
+        <v>4874.68</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>1320.97</v>
+        <v>7207.82</v>
       </c>
       <c r="Z85" s="35" t="n">
-        <v>5211.85</v>
+        <v>19062.49</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>1823.8</v>
+        <v>3621.89</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>1642.69</v>
+        <v>2250.21</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17089,78 +16849,78 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>95</v>
+        <v>4861.65</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>95</v>
+        <v>14727.4</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>6319.1</v>
+        <v>-308.41</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>300.92</v>
+        <v>20160.95</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>4095</v>
+        <v>21273.46</v>
       </c>
       <c r="K86" s="35" t="n">
-        <v>10810.02</v>
+        <v>55853.4</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>309.44</v>
+        <v>11149.11</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>309.28</v>
+        <v>19205.63</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>394.38</v>
+        <v>62888.84</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>3519.26</v>
+        <v>-4269.59</v>
       </c>
       <c r="P86" s="35" t="n">
-        <v>4532.36</v>
+        <v>88973.99000000001</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>4029.75</v>
+        <v>-4887.78</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>5506.28</v>
+        <v>5243.04</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>1193.71</v>
+        <v>-5169.97</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>1041.1</v>
+        <v>-8646.799999999999</v>
       </c>
       <c r="U86" s="35" t="n">
-        <v>11770.84</v>
+        <v>-13461.51</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>1035.89</v>
+        <v>-3440.56</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>3528.32</v>
+        <v>16064.18</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>3699.34</v>
+        <v>14746.44</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>3635.61</v>
+        <v>-14297.97</v>
       </c>
       <c r="Z86" s="35" t="n">
-        <v>11899.16</v>
+        <v>13072.09</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>3472.47</v>
+        <v>-4867.03</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>960.5700000000001</v>
+        <v>7456.99</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17182,63 +16942,71 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0</v>
+        <v>19500.28</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>6000</v>
+        <v>19300</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>4000</v>
+        <v>39337.34</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>7500</v>
+        <v>13607.98</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>7000</v>
+        <v>32151.63</v>
       </c>
       <c r="K87" s="35" t="n">
+        <v>104396.95</v>
+      </c>
+      <c r="L87" s="18" t="n">
+        <v>47748</v>
+      </c>
+      <c r="M87" s="18" t="n">
+        <v>36771.39</v>
+      </c>
+      <c r="N87" s="18" t="n">
+        <v>38966.42</v>
+      </c>
+      <c r="O87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="35" t="n">
+        <v>123485.81</v>
+      </c>
+      <c r="S87" s="18" t="n">
+        <v>45002.67</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>17000</v>
+      </c>
+      <c r="U87" s="9" t="n"/>
+      <c r="V87" s="18" t="n">
+        <v>261.95</v>
+      </c>
+      <c r="W87" s="18" t="n">
         <v>24500</v>
       </c>
-      <c r="L87" s="18" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N87" s="18" t="n">
+      <c r="X87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P87" s="35" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>3500</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S87" s="18" t="n">
+      <c r="Y87" s="18" t="n">
+        <v>43288.21</v>
+      </c>
+      <c r="Z87" s="35" t="n">
+        <v>68050.16</v>
+      </c>
+      <c r="AA87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="18" t="n">
-        <v>2200</v>
-      </c>
-      <c r="U87" s="35" t="n">
-        <v>10700</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="9" t="n"/>
-      <c r="AB87" s="5" t="n"/>
+      <c r="AB87" s="19" t="n">
+        <v>18299.9</v>
+      </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="11" t="n"/>
@@ -17259,42 +17027,79 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0</v>
+        <v>14400.28</v>
       </c>
       <c r="F88" s="9" t="n"/>
+      <c r="G88" s="18" t="n">
+        <v>10143.47</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>36406.57</v>
+      </c>
       <c r="I88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="9" t="n"/>
+        <v>12905.26</v>
+      </c>
+      <c r="K88" s="35" t="n">
+        <v>59455.3</v>
+      </c>
+      <c r="L88" s="18" t="n">
+        <v>45704.37</v>
+      </c>
+      <c r="M88" s="18" t="n">
+        <v>23638.07</v>
+      </c>
       <c r="N88" s="18" t="n">
-        <v>0</v>
+        <v>64500</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="9" t="n"/>
+        <v>2981.26</v>
+      </c>
+      <c r="P88" s="35" t="n">
+        <v>136823.7</v>
+      </c>
+      <c r="Q88" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>540.0599999999999</v>
+      </c>
       <c r="S88" s="18" t="n">
-        <v>0</v>
+        <v>47002.47</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="9" t="n"/>
+        <v>24700</v>
+      </c>
+      <c r="U88" s="35" t="n">
+        <v>72742.53</v>
+      </c>
+      <c r="V88" s="18" t="n">
+        <v>261.95</v>
+      </c>
+      <c r="W88" s="18" t="n">
+        <v>2500</v>
+      </c>
       <c r="X88" s="18" t="n">
-        <v>0</v>
+        <v>7416</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+        <v>44204.21</v>
+      </c>
+      <c r="Z88" s="35" t="n">
+        <v>54382.16</v>
+      </c>
+      <c r="AA88" s="18" t="n">
+        <v>416</v>
+      </c>
+      <c r="AB88" s="19" t="n">
+        <v>6715.9</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -17315,78 +17120,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>2528.86</v>
+        <v>486.55</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>-2598</v>
+        <v>547.58</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>-1151.85</v>
+        <v>634.99</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>7150.31</v>
+        <v>692.52</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>-1206.84</v>
+        <v>866.27</v>
       </c>
       <c r="K89" s="35" t="n">
-        <v>2193.62</v>
+        <v>2741.36</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>-6507.7</v>
+        <v>811.03</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>8808.1</v>
+        <v>842.89</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>20487.59</v>
+        <v>857.5</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>8450.41</v>
+        <v>863.65</v>
       </c>
       <c r="P89" s="35" t="n">
-        <v>31238.4</v>
+        <v>3375.07</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>-16546.84</v>
+        <v>1091.86</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>-9625.35</v>
+        <v>1228.2</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>-3306.9</v>
+        <v>1219.79</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>-6560.34</v>
+        <v>1333.44</v>
       </c>
       <c r="U89" s="35" t="n">
-        <v>-36039.43</v>
+        <v>4873.29</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>1978.82</v>
+        <v>1320.22</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>-6498.75</v>
+        <v>1290.28</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>6465.48</v>
+        <v>1280.38</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>9033.42</v>
+        <v>1320.97</v>
       </c>
       <c r="Z89" s="35" t="n">
-        <v>10978.97</v>
+        <v>5211.85</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>-1789.57</v>
+        <v>1823.8</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>-6979.81</v>
+        <v>1642.69</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17408,78 +17213,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>2428.42</v>
+        <v>95</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>20133.03</v>
+        <v>95</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-871.03</v>
+        <v>6319.1</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>7644.15</v>
+        <v>300.92</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-2491.58</v>
+        <v>4095</v>
       </c>
       <c r="K90" s="35" t="n">
-        <v>24414.57</v>
+        <v>10810.02</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>17940.93</v>
+        <v>309.44</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>8898.040000000001</v>
+        <v>309.28</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>21021.81</v>
+        <v>394.38</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>8087.96</v>
+        <v>3519.26</v>
       </c>
       <c r="P90" s="35" t="n">
-        <v>55948.74</v>
+        <v>4532.36</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>39907.26</v>
+        <v>4029.75</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>-9236.35</v>
+        <v>5506.28</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>-4192.04</v>
+        <v>1193.71</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>-4992.2</v>
+        <v>1041.1</v>
       </c>
       <c r="U90" s="35" t="n">
-        <v>21486.67</v>
+        <v>11770.84</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>24147.18</v>
+        <v>1035.89</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>-6931.21</v>
+        <v>3528.32</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>6303.43</v>
+        <v>3699.34</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>9326.450000000001</v>
+        <v>3635.61</v>
       </c>
       <c r="Z90" s="35" t="n">
-        <v>32845.85</v>
+        <v>11899.16</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>31798.82</v>
+        <v>3472.47</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>-6699.45</v>
+        <v>960.5700000000001</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -17501,29 +17306,63 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>7500</v>
+      </c>
       <c r="J91" s="18" t="n">
-        <v>352.39</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="U91" s="9" t="n"/>
-      <c r="X91" s="18" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K91" s="35" t="n">
+        <v>24500</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N91" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="O91" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P91" s="35" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q91" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>2200</v>
+      </c>
+      <c r="U91" s="35" t="n">
+        <v>10700</v>
+      </c>
       <c r="Y91" s="18" t="n">
-        <v>4996.88</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="9" t="n"/>
-      <c r="AA91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB91" s="5" t="n"/>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="11" t="n"/>
@@ -17544,13 +17383,37 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>사채의증가</t>
-        </is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="I92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K92" s="9" t="n"/>
+      <c r="N92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P92" s="9" t="n"/>
+      <c r="S92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="U92" s="9" t="n"/>
+      <c r="X92" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Y92" s="18" t="n">
         <v>0</v>
       </c>
@@ -17569,6 +17432,267 @@
       <c r="AM92" s="10" t="n"/>
       <c r="AN92" s="10" t="n"/>
       <c r="AO92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>2528.86</v>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="18" t="n">
+        <v>-2598</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>-1151.85</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>7150.31</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>-1206.84</v>
+      </c>
+      <c r="K93" s="35" t="n">
+        <v>2193.62</v>
+      </c>
+      <c r="L93" s="18" t="n">
+        <v>-6507.7</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>8808.1</v>
+      </c>
+      <c r="N93" s="18" t="n">
+        <v>20487.59</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>8450.41</v>
+      </c>
+      <c r="P93" s="35" t="n">
+        <v>31238.4</v>
+      </c>
+      <c r="Q93" s="18" t="n">
+        <v>-16546.84</v>
+      </c>
+      <c r="R93" s="18" t="n">
+        <v>-9625.35</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>-3306.9</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>-6560.34</v>
+      </c>
+      <c r="U93" s="35" t="n">
+        <v>-36039.43</v>
+      </c>
+      <c r="V93" s="18" t="n">
+        <v>1978.82</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>-6498.75</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>6465.48</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>9033.42</v>
+      </c>
+      <c r="Z93" s="35" t="n">
+        <v>10978.97</v>
+      </c>
+      <c r="AA93" s="18" t="n">
+        <v>-1789.57</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>-6979.81</v>
+      </c>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="11" t="n"/>
+      <c r="AK93" s="10" t="n"/>
+      <c r="AL93" s="10" t="n"/>
+      <c r="AM93" s="10" t="n"/>
+      <c r="AN93" s="10" t="n"/>
+      <c r="AO93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>2428.42</v>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>20133.03</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>-871.03</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>7644.15</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>-2491.58</v>
+      </c>
+      <c r="K94" s="35" t="n">
+        <v>24414.57</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>17940.93</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>8898.040000000001</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>21021.81</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>8087.96</v>
+      </c>
+      <c r="P94" s="35" t="n">
+        <v>55948.74</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>39907.26</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>-9236.35</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>-4192.04</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>-4992.2</v>
+      </c>
+      <c r="U94" s="35" t="n">
+        <v>21486.67</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>24147.18</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>-6931.21</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>6303.43</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>9326.450000000001</v>
+      </c>
+      <c r="Z94" s="35" t="n">
+        <v>32845.85</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>31798.82</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>-6699.45</v>
+      </c>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="11" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="10" t="n"/>
+      <c r="AM94" s="10" t="n"/>
+      <c r="AN94" s="10" t="n"/>
+      <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="J95" s="18" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="P95" s="9" t="n"/>
+      <c r="U95" s="9" t="n"/>
+      <c r="X95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>4996.88</v>
+      </c>
+      <c r="Z95" s="9" t="n"/>
+      <c r="AA95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="U96" s="9" t="n"/>
+      <c r="Y96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
+      <c r="AB96" s="5" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17829,7 +17953,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>73600</v>
+        <v>74900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5594,7 +5594,7 @@
         <v>81400</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>73800</v>
+        <v>77300</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>71050</v>
+        <v>72333.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>73600</v>
+        <v>74900</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.09219254975335942</v>
+        <v>0.0921925497533594</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.3532534155899174</v>
+        <v>0.3532534155899175</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01286700878303982</v>
+        <v>0.01286700878299971</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.04343059262769718</v>
+        <v>0.04343059262769036</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>259.06</v>
+        <v>263.64</v>
       </c>
     </row>
     <row r="32">
@@ -37973,7 +37973,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>74900</v>
+        <v>69400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>72333.3</v>
+        <v>71675</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>74900</v>
+        <v>69400</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 68,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 72,700원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>263.64</v>
+        <v>244.28</v>
       </c>
     </row>
     <row r="32">
@@ -37973,7 +37973,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>69400</v>
+        <v>63700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5685,7 +5685,7 @@
         <v>48100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>65500</v>
+        <v>62900</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>71675</v>
+        <v>69900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>69400</v>
+        <v>63700</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 72,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 74,400원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -35955,7 +35955,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37963,7 +37963,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>244.28</v>
+        <v>224.22</v>
       </c>
     </row>
     <row r="32">
@@ -37973,7 +37973,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>63700</v>
+        <v>63800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>69900</v>
+        <v>69920</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>63700</v>
+        <v>63800</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 74,400원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 68,500원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.09219254975335942</v>
+        <v>0.0921925497533594</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.3532534155899174</v>
+        <v>0.3532534155899175</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01286700878303982</v>
+        <v>0.01286700878299971</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.04343059262769718</v>
+        <v>0.04343059262769036</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>224.22</v>
+        <v>224.57</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>63800</v>
+        <v>62700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5685,7 +5685,7 @@
         <v>48100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>62900</v>
+        <v>61600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>69920</v>
+        <v>68716.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>63800</v>
+        <v>62700</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>224.57</v>
+        <v>220.7</v>
       </c>
     </row>
     <row r="32">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>62700</v>
+        <v>60500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5685,7 +5685,7 @@
         <v>48100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>61600</v>
+        <v>57400</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>68716.7</v>
+        <v>67500</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>62700</v>
+        <v>60500</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 68,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 63,000원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>220.7</v>
+        <v>212.95</v>
       </c>
     </row>
     <row r="32">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>60500</v>
+        <v>60600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>67500</v>
+        <v>66650</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>60500</v>
+        <v>60600</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>212.95</v>
+        <v>213.31</v>
       </c>
     </row>
     <row r="32">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>60600</v>
+        <v>60400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5685,7 +5685,7 @@
         <v>48100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>57400</v>
+        <v>53100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>66650</v>
+        <v>64027.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>60600</v>
+        <v>60400</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 63,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 54,500원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>213.31</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="32">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/189300_model.xlsx
+++ b/argus/kship/models/189300_model.xlsx
@@ -3664,7 +3664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4535,35 +4535,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4654,35 +4654,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4773,35 +4773,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -4892,35 +4892,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5011,35 +5011,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5130,35 +5130,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5249,35 +5249,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5368,35 +5368,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5503,7 +5503,7 @@
         <v>66500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>60400</v>
+        <v>51500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5685,7 +5685,7 @@
         <v>48100</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>53100</v>
+        <v>50600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5776,7 +5776,7 @@
         <v>66313.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>64027.3</v>
+        <v>61043.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8173,11 +8173,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>60400</v>
+        <v>51500</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 54,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 54,700원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38533,7 +38533,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>212.6</v>
+        <v>181.27</v>
       </c>
     </row>
     <row r="32">
@@ -38543,7 +38543,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="33">
